--- a/aircraft/reports/top-airlines-over-time-monthly.xlsx
+++ b/aircraft/reports/top-airlines-over-time-monthly.xlsx
@@ -10974,7 +10974,7 @@
         </is>
       </c>
       <c r="D659" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="660">
@@ -11022,7 +11022,7 @@
         </is>
       </c>
       <c r="D662" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="663">

--- a/aircraft/reports/top-airlines-over-time-monthly.xlsx
+++ b/aircraft/reports/top-airlines-over-time-monthly.xlsx
@@ -10974,7 +10974,7 @@
         </is>
       </c>
       <c r="D659" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="660">
@@ -11022,7 +11022,7 @@
         </is>
       </c>
       <c r="D662" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="663">

--- a/aircraft/reports/top-airlines-over-time-monthly.xlsx
+++ b/aircraft/reports/top-airlines-over-time-monthly.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D666"/>
+  <dimension ref="A1:D671"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11089,6 +11089,86 @@
         <v>7</v>
       </c>
     </row>
+    <row r="667">
+      <c r="A667" s="1" t="n">
+        <v>3545</v>
+      </c>
+      <c r="B667" s="2" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>Delta Air Lines</t>
+        </is>
+      </c>
+      <c r="D667" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" s="1" t="n">
+        <v>3546</v>
+      </c>
+      <c r="B668" s="2" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>EasyJet</t>
+        </is>
+      </c>
+      <c r="D668" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" s="1" t="n">
+        <v>3548</v>
+      </c>
+      <c r="B669" s="2" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>KLM</t>
+        </is>
+      </c>
+      <c r="D669" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" s="1" t="n">
+        <v>3552</v>
+      </c>
+      <c r="B670" s="2" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>Ryanair</t>
+        </is>
+      </c>
+      <c r="D670" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" s="1" t="n">
+        <v>3554</v>
+      </c>
+      <c r="B671" s="2" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>United Airlines</t>
+        </is>
+      </c>
+      <c r="D671" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/aircraft/reports/top-airlines-over-time-monthly.xlsx
+++ b/aircraft/reports/top-airlines-over-time-monthly.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D671"/>
+  <dimension ref="A1:D672"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11118,7 +11118,7 @@
         </is>
       </c>
       <c r="D668" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="669">
@@ -11130,42 +11130,58 @@
       </c>
       <c r="C669" t="inlineStr">
         <is>
-          <t>KLM</t>
+          <t>Jet2</t>
         </is>
       </c>
       <c r="D669" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" s="1" t="n">
-        <v>3552</v>
+        <v>3549</v>
       </c>
       <c r="B670" s="2" t="n">
         <v>45901</v>
       </c>
       <c r="C670" t="inlineStr">
         <is>
-          <t>Ryanair</t>
+          <t>KLM</t>
         </is>
       </c>
       <c r="D670" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" s="1" t="n">
-        <v>3554</v>
+        <v>3553</v>
       </c>
       <c r="B671" s="2" t="n">
         <v>45901</v>
       </c>
       <c r="C671" t="inlineStr">
         <is>
+          <t>Ryanair</t>
+        </is>
+      </c>
+      <c r="D671" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" s="1" t="n">
+        <v>3556</v>
+      </c>
+      <c r="B672" s="2" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
           <t>United Airlines</t>
         </is>
       </c>
-      <c r="D671" t="n">
+      <c r="D672" t="n">
         <v>2</v>
       </c>
     </row>

--- a/aircraft/reports/top-airlines-over-time-monthly.xlsx
+++ b/aircraft/reports/top-airlines-over-time-monthly.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D672"/>
+  <dimension ref="A1:D673"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11091,7 +11091,7 @@
     </row>
     <row r="667">
       <c r="A667" s="1" t="n">
-        <v>3545</v>
+        <v>3546</v>
       </c>
       <c r="B667" s="2" t="n">
         <v>45901</v>
@@ -11107,7 +11107,7 @@
     </row>
     <row r="668">
       <c r="A668" s="1" t="n">
-        <v>3546</v>
+        <v>3547</v>
       </c>
       <c r="B668" s="2" t="n">
         <v>45901</v>
@@ -11123,7 +11123,7 @@
     </row>
     <row r="669">
       <c r="A669" s="1" t="n">
-        <v>3548</v>
+        <v>3550</v>
       </c>
       <c r="B669" s="2" t="n">
         <v>45901</v>
@@ -11139,7 +11139,7 @@
     </row>
     <row r="670">
       <c r="A670" s="1" t="n">
-        <v>3549</v>
+        <v>3551</v>
       </c>
       <c r="B670" s="2" t="n">
         <v>45901</v>
@@ -11155,34 +11155,50 @@
     </row>
     <row r="671">
       <c r="A671" s="1" t="n">
-        <v>3553</v>
+        <v>3552</v>
       </c>
       <c r="B671" s="2" t="n">
         <v>45901</v>
       </c>
       <c r="C671" t="inlineStr">
         <is>
-          <t>Ryanair</t>
+          <t>Lufthansa</t>
         </is>
       </c>
       <c r="D671" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" s="1" t="n">
-        <v>3556</v>
+        <v>3558</v>
       </c>
       <c r="B672" s="2" t="n">
         <v>45901</v>
       </c>
       <c r="C672" t="inlineStr">
         <is>
+          <t>Ryanair</t>
+        </is>
+      </c>
+      <c r="D672" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" s="1" t="n">
+        <v>3562</v>
+      </c>
+      <c r="B673" s="2" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
           <t>United Airlines</t>
         </is>
       </c>
-      <c r="D672" t="n">
-        <v>2</v>
+      <c r="D673" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
